--- a/bao-gia/BLT/MEGA/Bao-gia-BLT-MEGA-BG-2026-001-Viet-Trung.xlsx
+++ b/bao-gia/BLT/MEGA/Bao-gia-BLT-MEGA-BG-2026-001-Viet-Trung.xlsx
@@ -10,8 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Báo giá" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Báo giá'!$21:$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Báo giá'!$A$1:$G$71</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Báo giá'!$19:$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Báo giá'!$A$1:$G$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,7 +34,13 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="000D2B66"/>
-      <sz val="16"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -45,13 +51,13 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="000D2B66"/>
-      <sz val="22"/>
+      <sz val="20"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -74,6 +80,11 @@
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001F4FBF"/>
       <sz val="9.5"/>
     </font>
     <font>
@@ -270,29 +281,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -316,94 +333,94 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -489,9 +506,9 @@
       <col>0</col>
       <colOff>19050</colOff>
       <row>0</row>
-      <rowOff>28575</rowOff>
+      <rowOff>133350</rowOff>
     </from>
-    <ext cx="876300" cy="876300"/>
+    <ext cx="800100" cy="800100"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -801,19 +818,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="38.5" customWidth="1" min="2" max="2"/>
+    <col width="9.5" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="14.5" customWidth="1" min="5" max="5"/>
     <col width="16.5" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH KỸ THUẬT CÔNG TRÌNH BLT</t>
@@ -821,110 +838,183 @@
       </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Địa chỉ / 地址: Số 2A đường Nguyễn Khánh Toàn, khối Trường Phúc, phường Trường Vinh, tỉnh Nghệ An, Việt Nam</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>BẢNG BÁO GIÁ</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>BLT工程技术有限公司</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>报价单  ·  QUOTATION</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>MST / 税号: 2902269718   |   Điện thoại / 电话: 0984 586 089</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>MST / 税号: 2902269718</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00595959"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">Số báo giá / 报价编号: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00000000"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t>BG-2026/001</t>
+          </r>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Điện thoại / 电话: 0984 586 089</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00595959"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">Ngày báo giá / 报价日期: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t>10/10/2026</t>
+          </r>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Email / 邮箱: hobinh150589@gmail.com</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="10" customHeight="1">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="10" customHeight="1"/>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>BẢNG BÁO GIÁ</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>报价单</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="10" customHeight="1"/>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>THÔNG TIN KHÁCH HÀNG / 客户信息</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>THÔNG TIN BÁO GIÁ / 报价信息</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="9" t="n"/>
-    </row>
-    <row r="12" ht="17.5" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00595959"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">Hiệu lực / 有效期: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t>30 ngày / 30天</t>
+          </r>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="10" customHeight="1">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="10" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>BÊN BÁO GIÁ / 报价方</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>KÍNH GỬI KHÁCH HÀNG / 致客户</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="11" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00595959"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">Địa chỉ / 地址: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t>Số 2A đường Nguyễn Khánh Toàn, khối Trường Phúc, phường Trường Vinh, tỉnh Nghệ An, Việt Nam</t>
+          </r>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -945,34 +1035,25 @@
           </r>
         </is>
       </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <color rgb="00595959"/>
-              <sz val="9.5"/>
-            </rPr>
-            <t xml:space="preserve">Số báo giá / 报价编号: </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
               <color rgb="00000000"/>
               <sz val="9.5"/>
             </rPr>
-            <t>BG-2026/001</t>
+            <t>越南义安省长荣坊长福区阮庆全路2A号</t>
           </r>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="12" t="n"/>
-    </row>
-    <row r="13" ht="17.5" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -984,85 +1065,11 @@
           </r>
         </is>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00595959"/>
-              <sz val="9.5"/>
-            </rPr>
-            <t xml:space="preserve">Ngày báo giá / 报价日期: </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="9.5"/>
-            </rPr>
-            <t>10/10/2026</t>
-          </r>
-        </is>
-      </c>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="12" t="n"/>
-    </row>
-    <row r="14" ht="17.5" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00595959"/>
-              <sz val="9.5"/>
-            </rPr>
-            <t xml:space="preserve">Điện thoại / 电话: </t>
-          </r>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00595959"/>
-              <sz val="9.5"/>
-            </rPr>
-            <t xml:space="preserve">Hiệu lực / 有效期: </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="9.5"/>
-            </rPr>
-            <t>30 ngày / 30天</t>
-          </r>
-        </is>
-      </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="12" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00595959"/>
-              <sz val="9.5"/>
-            </rPr>
-            <t xml:space="preserve">Địa chỉ / 地址: </t>
-          </r>
-        </is>
-      </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1078,16 +1085,68 @@
               <color rgb="00000000"/>
               <sz val="9.5"/>
             </rPr>
-            <t>HỒ VĂN BÌNH – 0984 586 089</t>
+            <t>HỒ VĂN BÌNH – Giám đốc</t>
           </r>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16" ht="10" customHeight="1"/>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00595959"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">Điện thoại / 电话: </t>
+          </r>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00595959"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">Số tài khoản / 银行账号: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t>1066217478 – Vietcombank</t>
+          </r>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00595959"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">Địa chỉ / 地址: </t>
+          </r>
+        </is>
+      </c>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="10" customHeight="1"/>
+    <row r="15" ht="47" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1118,1176 +1177,1180 @@
           </r>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="16" t="n"/>
-    </row>
-    <row r="18" ht="10" customHeight="1"/>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+    </row>
+    <row r="16" ht="10" customHeight="1"/>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH KỸ THUẬT CÔNG TRÌNH BLT trân trọng cảm ơn Quý khách đã quan tâm. Chúng tôi xin gửi tới Quý khách bảng báo giá cho công trình nêu trên như sau:
-我司衷心感谢贵方的关注，现将上述工程报价如下：</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="17" t="n"/>
-    </row>
-    <row r="20" ht="8" customHeight="1"/>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+BLT工程技术有限公司衷心感谢贵公司的关注。现就上述工程向贵公司报价如下：</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="8" customHeight="1"/>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>STT
 序号</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Tên hàng hóa / Quy cách kỹ thuật
 货物名称 / 技术规格</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>ĐVT
 单位</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>Số lượng
 数量</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>Đơn giá (VNĐ)
 单价(越南盾)</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>Thành tiền (VNĐ)
 金额(越南盾)</t>
         </is>
       </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>Ghi chú
 备注</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>Tủ điện, tủ điều khiển
 配电箱及控制柜</t>
         </is>
       </c>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-    </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="21" t="n">
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Tủ đồng hồ điện thông minh (gồm đồng hồ điện đa năng, biến dòng, cầu đấu dây; lắp treo tường)
 智能电表箱（含多功能电表、互感器、接线端子等；悬挂式）</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>Tủ
 台</t>
         </is>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D21" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E21" s="25" t="n">
         <v>7700000</v>
       </c>
-      <c r="F23" s="24">
-        <f>IF(OR(D23="",E23=""),"",ROUND(D23*E23,0))</f>
-        <v/>
-      </c>
-      <c r="G23" s="25" t="inlineStr">
+      <c r="F21" s="26">
+        <f>IF(OR(D21="",E21=""),"",ROUND(D21*E21,0))</f>
+        <v/>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
         <is>
           <t>Acrel</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="26" t="n">
+    <row r="22" ht="66" customHeight="1">
+      <c r="A22" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>Tủ điều khiển biến tần bơm nước lạnh ACPL-01 (tủ kiểu Rittal 1800×1000×800, đặt sàn)
 冷冻水泵变频控制柜 ACPL-01（仿威图机柜1800×1000×800，落地式）</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>Tủ
 台</t>
         </is>
       </c>
-      <c r="D24" s="28" t="n">
+      <c r="D22" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="28" t="n">
+      <c r="E22" s="30" t="n">
         <v>220000000</v>
       </c>
-      <c r="F24" s="29">
-        <f>IF(OR(D24="",E24=""),"",ROUND(D24*E24,0))</f>
-        <v/>
-      </c>
-      <c r="G24" s="30" t="inlineStr">
+      <c r="F22" s="31">
+        <f>IF(OR(D22="",E22=""),"",ROUND(D22*E22,0))</f>
+        <v/>
+      </c>
+      <c r="G22" s="32" t="inlineStr">
         <is>
           <t>ABB, Schneider; Acrel</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="21" t="n">
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Tủ điều khiển biến tần bơm nước lạnh ACPL-02 (tủ kiểu Rittal 1800×1000×800, đặt sàn)
 冷冻水泵变频控制柜 ACPL-02（仿威图机柜1800×1000×800，落地式）</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>Tủ
 台</t>
         </is>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D23" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E23" s="25" t="n">
         <v>220000000</v>
       </c>
-      <c r="F25" s="24">
-        <f>IF(OR(D25="",E25=""),"",ROUND(D25*E25,0))</f>
-        <v/>
-      </c>
-      <c r="G25" s="25" t="inlineStr">
+      <c r="F23" s="26">
+        <f>IF(OR(D23="",E23=""),"",ROUND(D23*E23,0))</f>
+        <v/>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
         <is>
           <t>ABB, Schneider; Acrel</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="26" t="n">
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>Tủ điều khiển biến tần bơm nước giải nhiệt ACPL-03 (tủ kiểu Rittal 1800×1000×800, đặt sàn)
 冷却水泵变频控制柜 ACPL-03（仿威图机柜1800×1000×800，落地式）</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>Tủ
 台</t>
         </is>
       </c>
-      <c r="D26" s="28" t="n">
+      <c r="D24" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="28" t="n">
+      <c r="E24" s="30" t="n">
         <v>220000000</v>
       </c>
-      <c r="F26" s="29">
-        <f>IF(OR(D26="",E26=""),"",ROUND(D26*E26,0))</f>
-        <v/>
-      </c>
-      <c r="G26" s="30" t="inlineStr">
+      <c r="F24" s="31">
+        <f>IF(OR(D24="",E24=""),"",ROUND(D24*E24,0))</f>
+        <v/>
+      </c>
+      <c r="G24" s="32" t="inlineStr">
         <is>
           <t>ABB, Schneider; Acrel</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="54" customHeight="1">
-      <c r="A27" s="21" t="n">
+    <row r="25" ht="66" customHeight="1">
+      <c r="A25" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Tủ điều khiển biến tần bơm nước giải nhiệt ACPL-04 (tủ kiểu Rittal 1800×1000×800, đặt sàn)
 冷却水泵变频控制柜 ACPL-04（仿威图机柜1800×1000×800，落地式）</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>Tủ
 台</t>
         </is>
       </c>
-      <c r="D27" s="23" t="n">
+      <c r="D25" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="23" t="n">
+      <c r="E25" s="25" t="n">
         <v>203500000</v>
       </c>
-      <c r="F27" s="24">
-        <f>IF(OR(D27="",E27=""),"",ROUND(D27*E27,0))</f>
-        <v/>
-      </c>
-      <c r="G27" s="25" t="inlineStr">
+      <c r="F25" s="26">
+        <f>IF(OR(D25="",E25=""),"",ROUND(D25*E25,0))</f>
+        <v/>
+      </c>
+      <c r="G25" s="27" t="inlineStr">
         <is>
           <t>ABB, Schneider; Acrel</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="54" customHeight="1">
-      <c r="A28" s="26" t="n">
+    <row r="26" ht="66" customHeight="1">
+      <c r="A26" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>Tủ điều khiển biến tần tháp giải nhiệt ACPL-05 (tủ kiểu Rittal 1800×1200×800, đặt sàn)
 冷却塔变频控制柜 ACPL-05（仿威图机柜1800×1200×800，落地式）</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>Tủ
 台</t>
         </is>
       </c>
-      <c r="D28" s="28" t="n">
+      <c r="D26" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="28" t="n">
+      <c r="E26" s="30" t="n">
         <v>181500000</v>
       </c>
-      <c r="F28" s="29">
-        <f>IF(OR(D28="",E28=""),"",ROUND(D28*E28,0))</f>
-        <v/>
-      </c>
-      <c r="G28" s="30" t="inlineStr">
+      <c r="F26" s="31">
+        <f>IF(OR(D26="",E26=""),"",ROUND(D26*E26,0))</f>
+        <v/>
+      </c>
+      <c r="G26" s="32" t="inlineStr">
         <is>
           <t>ABB, Schneider; Acrel</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="54" customHeight="1">
-      <c r="A29" s="21" t="n">
+    <row r="27" ht="66" customHeight="1">
+      <c r="A27" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Tủ điều khiển biến tần tháp giải nhiệt ACPL-06 (tủ kiểu Rittal 1800×800×800, đặt sàn)
 冷却塔变频控制柜 ACPL-06（仿威图机柜1800×800×800，落地式）</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>Tủ
 台</t>
         </is>
       </c>
-      <c r="D29" s="23" t="n">
+      <c r="D27" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="23" t="n">
+      <c r="E27" s="25" t="n">
         <v>165000000</v>
       </c>
-      <c r="F29" s="24">
-        <f>IF(OR(D29="",E29=""),"",ROUND(D29*E29,0))</f>
-        <v/>
-      </c>
-      <c r="G29" s="25" t="inlineStr">
+      <c r="F27" s="26">
+        <f>IF(OR(D27="",E27=""),"",ROUND(D27*E27,0))</f>
+        <v/>
+      </c>
+      <c r="G27" s="27" t="inlineStr">
         <is>
           <t>ABB, Schneider; Acrel</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="54" customHeight="1">
-      <c r="A30" s="26" t="n">
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>Tủ điều khiển van điện ACPL-07 (tủ kiểu Rittal 1800×800×800, đặt sàn)
 电动阀门控制柜 ACPL-07（仿威图机柜1800×800×800，落地式）</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>Tủ
 台</t>
         </is>
       </c>
-      <c r="D30" s="28" t="n">
+      <c r="D28" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="28" t="n">
+      <c r="E28" s="30" t="n">
         <v>154000000</v>
       </c>
-      <c r="F30" s="29">
-        <f>IF(OR(D30="",E30=""),"",ROUND(D30*E30,0))</f>
-        <v/>
-      </c>
-      <c r="G30" s="30" t="inlineStr">
+      <c r="F28" s="31">
+        <f>IF(OR(D28="",E28=""),"",ROUND(D28*E28,0))</f>
+        <v/>
+      </c>
+      <c r="G28" s="32" t="inlineStr">
         <is>
           <t>ABB, Schneider; Acrel</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>Cáp điện, cáp điều khiển
 电力电缆及控制线缆</t>
         </is>
       </c>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="20" t="n"/>
-      <c r="G31" s="20" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="21" t="n">
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Cáp điện động lực lõi đồng YJV-3×70+1×35
 电力电缆 铜芯 YJV-3×70+1×35</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D32" s="23" t="n">
+      <c r="D30" s="25" t="n">
         <v>129</v>
       </c>
-      <c r="E32" s="23" t="n">
+      <c r="E30" s="25" t="n">
         <v>1650000</v>
       </c>
-      <c r="F32" s="24">
-        <f>IF(OR(D32="",E32=""),"",ROUND(D32*E32,0))</f>
-        <v/>
-      </c>
-      <c r="G32" s="25" t="inlineStr">
+      <c r="F30" s="26">
+        <f>IF(OR(D30="",E30=""),"",ROUND(D30*E30,0))</f>
+        <v/>
+      </c>
+      <c r="G30" s="27" t="inlineStr">
         <is>
           <t>Chengtiantai, Nanyang, LS, Taya</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="26" t="n">
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>Cáp điện động lực lõi đồng YJV-3×50+1×25
 电力电缆 铜芯 YJV-3×50+1×25</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D33" s="28" t="n">
+      <c r="D31" s="30" t="n">
         <v>213</v>
       </c>
-      <c r="E33" s="28" t="n">
+      <c r="E31" s="30" t="n">
         <v>1210000</v>
       </c>
-      <c r="F33" s="29">
-        <f>IF(OR(D33="",E33=""),"",ROUND(D33*E33,0))</f>
-        <v/>
-      </c>
-      <c r="G33" s="30" t="inlineStr">
+      <c r="F31" s="31">
+        <f>IF(OR(D31="",E31=""),"",ROUND(D31*E31,0))</f>
+        <v/>
+      </c>
+      <c r="G31" s="32" t="inlineStr">
         <is>
           <t>Chengtiantai, Nanyang, LS, Taya</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="21" t="n">
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>Cáp điện động lực lõi đồng YJV-3×10+1×6
 电力电缆 铜芯 YJV-3×10+1×6</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D34" s="23" t="n">
+      <c r="D32" s="25" t="n">
         <v>542</v>
       </c>
-      <c r="E34" s="23" t="n">
+      <c r="E32" s="25" t="n">
         <v>462000</v>
       </c>
-      <c r="F34" s="24">
-        <f>IF(OR(D34="",E34=""),"",ROUND(D34*E34,0))</f>
-        <v/>
-      </c>
-      <c r="G34" s="25" t="inlineStr">
+      <c r="F32" s="26">
+        <f>IF(OR(D32="",E32=""),"",ROUND(D32*E32,0))</f>
+        <v/>
+      </c>
+      <c r="G32" s="27" t="inlineStr">
         <is>
           <t>Chengtiantai, Nanyang, LS, Taya</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="26" t="n">
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="B35" s="27" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>Cáp điện động lực lõi đồng YJV-5×2.5
 电力电缆 铜芯 YJV-5×2.5</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D35" s="28" t="n">
+      <c r="D33" s="30" t="n">
         <v>58</v>
       </c>
-      <c r="E35" s="28" t="n">
+      <c r="E33" s="30" t="n">
         <v>374000</v>
       </c>
-      <c r="F35" s="29">
-        <f>IF(OR(D35="",E35=""),"",ROUND(D35*E35,0))</f>
-        <v/>
-      </c>
-      <c r="G35" s="30" t="inlineStr">
+      <c r="F33" s="31">
+        <f>IF(OR(D33="",E33=""),"",ROUND(D33*E33,0))</f>
+        <v/>
+      </c>
+      <c r="G33" s="32" t="inlineStr">
         <is>
           <t>Chengtiantai, Nanyang, LS, Taya</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="21" t="n">
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>Cáp điện động lực lõi đồng YJV-4×2.5
 电力电缆 铜芯 YJV-4×2.5</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D36" s="23" t="n">
+      <c r="D34" s="25" t="n">
         <v>884</v>
       </c>
-      <c r="E36" s="23" t="n">
+      <c r="E34" s="25" t="n">
         <v>297000</v>
       </c>
-      <c r="F36" s="24">
-        <f>IF(OR(D36="",E36=""),"",ROUND(D36*E36,0))</f>
-        <v/>
-      </c>
-      <c r="G36" s="25" t="inlineStr">
+      <c r="F34" s="26">
+        <f>IF(OR(D34="",E34=""),"",ROUND(D34*E34,0))</f>
+        <v/>
+      </c>
+      <c r="G34" s="27" t="inlineStr">
         <is>
           <t>Chengtiantai, Nanyang, LS, Taya</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="26" t="n">
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B37" s="27" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>Cáp điện động lực lõi đồng YJV-3×2.5
 电力电缆 铜芯 YJV-3×2.5</t>
         </is>
       </c>
-      <c r="C37" s="26" t="inlineStr">
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D37" s="28" t="n">
+      <c r="D35" s="30" t="n">
         <v>87</v>
       </c>
-      <c r="E37" s="28" t="n">
+      <c r="E35" s="30" t="n">
         <v>231000</v>
       </c>
-      <c r="F37" s="29">
-        <f>IF(OR(D37="",E37=""),"",ROUND(D37*E37,0))</f>
-        <v/>
-      </c>
-      <c r="G37" s="30" t="inlineStr">
+      <c r="F35" s="31">
+        <f>IF(OR(D35="",E35=""),"",ROUND(D35*E35,0))</f>
+        <v/>
+      </c>
+      <c r="G35" s="32" t="inlineStr">
         <is>
           <t>Chengtiantai, Nanyang, LS, Taya</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="21" t="n">
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B36" s="24" t="inlineStr">
         <is>
           <t>Cáp điều khiển lõi đồng RVV-3×1.0
 控制线缆 铜芯 RVV-3×1.0</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D38" s="23" t="n">
+      <c r="D36" s="25" t="n">
         <v>1031</v>
       </c>
-      <c r="E38" s="23" t="n">
+      <c r="E36" s="25" t="n">
         <v>165000</v>
       </c>
-      <c r="F38" s="24">
-        <f>IF(OR(D38="",E38=""),"",ROUND(D38*E38,0))</f>
-        <v/>
-      </c>
-      <c r="G38" s="25" t="inlineStr">
+      <c r="F36" s="26">
+        <f>IF(OR(D36="",E36=""),"",ROUND(D36*E36,0))</f>
+        <v/>
+      </c>
+      <c r="G36" s="27" t="inlineStr">
         <is>
           <t>Chengtiantai, Nanyang, LS, Taya</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>III</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>Máng cáp, ống luồn dây, giá đỡ
 线槽、线管及支吊架</t>
         </is>
       </c>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="20" t="n"/>
-      <c r="G39" s="20" t="n"/>
-    </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="26" t="n">
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="22" t="n"/>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="28" t="n">
         <v>16</v>
       </c>
-      <c r="B40" s="27" t="inlineStr">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>Máng cáp thép mạ kẽm 800×200×1.5mm (gồm phụ kiện)
 镀锌线槽 800×200×1.5mm（镀锌钢板，含配件）</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="C38" s="28" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D40" s="28" t="n">
+      <c r="D38" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="E40" s="28" t="n">
+      <c r="E38" s="30" t="n">
         <v>1518000</v>
       </c>
-      <c r="F40" s="29">
-        <f>IF(OR(D40="",E40=""),"",ROUND(D40*E40,0))</f>
-        <v/>
-      </c>
-      <c r="G40" s="30" t="inlineStr">
+      <c r="F38" s="31">
+        <f>IF(OR(D38="",E38=""),"",ROUND(D38*E38,0))</f>
+        <v/>
+      </c>
+      <c r="G38" s="32" t="inlineStr">
         <is>
           <t>Hàng trong nước
 国产优质</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="21" t="n">
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="B41" s="22" t="inlineStr">
+      <c r="B39" s="24" t="inlineStr">
         <is>
           <t>Máng cáp thép mạ kẽm 400×200×1.2mm (gồm phụ kiện)
 镀锌线槽 400×200×1.2mm（镀锌钢板，含配件）</t>
         </is>
       </c>
-      <c r="C41" s="21" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D41" s="23" t="n">
+      <c r="D39" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="E41" s="23" t="n">
+      <c r="E39" s="25" t="n">
         <v>1320000</v>
       </c>
-      <c r="F41" s="24">
-        <f>IF(OR(D41="",E41=""),"",ROUND(D41*E41,0))</f>
-        <v/>
-      </c>
-      <c r="G41" s="25" t="inlineStr">
+      <c r="F39" s="26">
+        <f>IF(OR(D39="",E39=""),"",ROUND(D39*E39,0))</f>
+        <v/>
+      </c>
+      <c r="G39" s="27" t="inlineStr">
         <is>
           <t>Hàng trong nước
 国产优质</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="26" t="n">
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="28" t="n">
         <v>18</v>
       </c>
-      <c r="B42" s="27" t="inlineStr">
+      <c r="B40" s="29" t="inlineStr">
         <is>
           <t>Máng cáp thép mạ kẽm 300×150×1.2mm (gồm phụ kiện)
 镀锌线槽 300×150×1.2mm（镀锌钢板，含配件）</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="C40" s="28" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D42" s="28" t="n">
+      <c r="D40" s="30" t="n">
         <v>52</v>
       </c>
-      <c r="E42" s="28" t="n">
+      <c r="E40" s="30" t="n">
         <v>880000</v>
       </c>
-      <c r="F42" s="29">
-        <f>IF(OR(D42="",E42=""),"",ROUND(D42*E42,0))</f>
-        <v/>
-      </c>
-      <c r="G42" s="30" t="inlineStr">
+      <c r="F40" s="31">
+        <f>IF(OR(D40="",E40=""),"",ROUND(D40*E40,0))</f>
+        <v/>
+      </c>
+      <c r="G40" s="32" t="inlineStr">
         <is>
           <t>Hàng trong nước
 国产优质</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="21" t="n">
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="B43" s="22" t="inlineStr">
+      <c r="B41" s="24" t="inlineStr">
         <is>
           <t>Máng cáp thép mạ kẽm 200×100×1.0mm (gồm phụ kiện)
 镀锌线槽 200×100×1.0mm（镀锌钢板，含配件）</t>
         </is>
       </c>
-      <c r="C43" s="21" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D43" s="23" t="n">
+      <c r="D41" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="E43" s="23" t="n">
+      <c r="E41" s="25" t="n">
         <v>550000</v>
       </c>
-      <c r="F43" s="24">
-        <f>IF(OR(D43="",E43=""),"",ROUND(D43*E43,0))</f>
-        <v/>
-      </c>
-      <c r="G43" s="25" t="inlineStr">
+      <c r="F41" s="26">
+        <f>IF(OR(D41="",E41=""),"",ROUND(D41*E41,0))</f>
+        <v/>
+      </c>
+      <c r="G41" s="27" t="inlineStr">
         <is>
           <t>Hàng trong nước
 国产优质</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="26" t="n">
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="B44" s="27" t="inlineStr">
+      <c r="B42" s="29" t="inlineStr">
         <is>
           <t>Máng cáp thép mạ kẽm 150×100×1.0mm (gồm phụ kiện)
 镀锌线槽 150×100×1.0mm（镀锌钢板，含配件）</t>
         </is>
       </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="C42" s="28" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D44" s="28" t="n">
+      <c r="D42" s="30" t="n">
         <v>34</v>
       </c>
-      <c r="E44" s="28" t="n">
+      <c r="E42" s="30" t="n">
         <v>517000</v>
       </c>
-      <c r="F44" s="29">
-        <f>IF(OR(D44="",E44=""),"",ROUND(D44*E44,0))</f>
-        <v/>
-      </c>
-      <c r="G44" s="30" t="inlineStr">
+      <c r="F42" s="31">
+        <f>IF(OR(D42="",E42=""),"",ROUND(D42*E42,0))</f>
+        <v/>
+      </c>
+      <c r="G42" s="32" t="inlineStr">
         <is>
           <t>Hàng trong nước
 国产优质</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="21" t="n">
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="B45" s="22" t="inlineStr">
+      <c r="B43" s="24" t="inlineStr">
         <is>
           <t>Ống luồn dây điện PVC cứng U-PVC Φ25 (gồm phụ kiện)
 PVC线管 U-PVC硬管 Φ25（含配件）</t>
         </is>
       </c>
-      <c r="C45" s="21" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>m
 米</t>
         </is>
       </c>
-      <c r="D45" s="23" t="n">
+      <c r="D43" s="25" t="n">
         <v>104</v>
       </c>
-      <c r="E45" s="23" t="n">
+      <c r="E43" s="25" t="n">
         <v>198000</v>
       </c>
-      <c r="F45" s="24">
-        <f>IF(OR(D45="",E45=""),"",ROUND(D45*E45,0))</f>
-        <v/>
-      </c>
-      <c r="G45" s="25" t="inlineStr">
+      <c r="F43" s="26">
+        <f>IF(OR(D43="",E43=""),"",ROUND(D43*E43,0))</f>
+        <v/>
+      </c>
+      <c r="G43" s="27" t="inlineStr">
         <is>
           <t>Lesso, Rifeng</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="26" t="n">
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="B46" s="27" t="inlineStr">
+      <c r="B44" s="29" t="inlineStr">
         <is>
           <t>Giá treo đỡ máng cáp, ống luồn dây (thép góc, ty ren)
 线槽、线管支吊架（角钢、丝杆）</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="C44" s="28" t="inlineStr">
         <is>
           <t>kg
 千克</t>
         </is>
       </c>
-      <c r="D46" s="31" t="n">
+      <c r="D44" s="33" t="n">
         <v>610.7</v>
       </c>
-      <c r="E46" s="28" t="n">
+      <c r="E44" s="30" t="n">
         <v>275000</v>
       </c>
-      <c r="F46" s="29">
-        <f>IF(OR(D46="",E46=""),"",ROUND(D46*E46,0))</f>
-        <v/>
-      </c>
-      <c r="G46" s="30" t="inlineStr">
+      <c r="F44" s="31">
+        <f>IF(OR(D44="",E44=""),"",ROUND(D44*E44,0))</f>
+        <v/>
+      </c>
+      <c r="G44" s="32" t="inlineStr">
         <is>
           <t>Tiêu chuẩn GB
 国标</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="19" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>IV</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B45" s="22" t="inlineStr">
         <is>
           <t>Vật tư phụ và đấu nối
 安装辅材及接线</t>
         </is>
       </c>
-      <c r="C47" s="20" t="n"/>
-      <c r="D47" s="20" t="n"/>
-      <c r="E47" s="20" t="n"/>
-      <c r="F47" s="20" t="n"/>
-      <c r="G47" s="20" t="n"/>
-    </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="21" t="n">
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B46" s="24" t="inlineStr">
         <is>
           <t>Vật tư phụ lắp đặt (đầu cos, dây rút, băng keo điện...)
 安装辅材（线耳、扎带、电工胶布等）</t>
         </is>
       </c>
-      <c r="C48" s="21" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
         <is>
           <t>Gói
 项</t>
         </is>
       </c>
-      <c r="D48" s="23" t="n">
+      <c r="D46" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="23" t="n">
+      <c r="E46" s="25" t="n">
         <v>110000000</v>
       </c>
-      <c r="F48" s="24">
-        <f>IF(OR(D48="",E48=""),"",ROUND(D48*E48,0))</f>
-        <v/>
-      </c>
-      <c r="G48" s="25" t="inlineStr"/>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="26" t="n">
+      <c r="F46" s="26">
+        <f>IF(OR(D46="",E46=""),"",ROUND(D46*E46,0))</f>
+        <v/>
+      </c>
+      <c r="G46" s="27" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="28" t="n">
         <v>24</v>
       </c>
-      <c r="B49" s="27" t="inlineStr">
+      <c r="B47" s="29" t="inlineStr">
         <is>
           <t>Đấu nối dây cụm máy làm lạnh nước (chiller)
 冷水机组接线</t>
         </is>
       </c>
-      <c r="C49" s="26" t="inlineStr">
+      <c r="C47" s="28" t="inlineStr">
         <is>
           <t>Máy
 台</t>
         </is>
       </c>
-      <c r="D49" s="28" t="n">
+      <c r="D47" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="E49" s="28" t="n">
+      <c r="E47" s="30" t="n">
         <v>22000000</v>
       </c>
-      <c r="F49" s="29">
-        <f>IF(OR(D49="",E49=""),"",ROUND(D49*E49,0))</f>
-        <v/>
-      </c>
-      <c r="G49" s="30" t="inlineStr"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="32" t="inlineStr">
+      <c r="F47" s="31">
+        <f>IF(OR(D47="",E47=""),"",ROUND(D47*E47,0))</f>
+        <v/>
+      </c>
+      <c r="G47" s="32" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t>Cộng tiền hàng (chưa VAT) / 货款合计（不含税）</t>
         </is>
       </c>
-      <c r="B50" s="32" t="n"/>
-      <c r="C50" s="32" t="n"/>
-      <c r="D50" s="32" t="n"/>
-      <c r="E50" s="32" t="n"/>
-      <c r="F50" s="33">
-        <f>SUM(F22:F49)</f>
-        <v/>
-      </c>
-      <c r="G50" s="34" t="n"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="35" t="inlineStr">
+      <c r="B48" s="34" t="n"/>
+      <c r="C48" s="34" t="n"/>
+      <c r="D48" s="34" t="n"/>
+      <c r="E48" s="34" t="n"/>
+      <c r="F48" s="35">
+        <f>SUM(F20:F47)</f>
+        <v/>
+      </c>
+      <c r="G48" s="36" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="37" t="inlineStr">
         <is>
           <t>Thuế GTGT (VAT) / 增值税</t>
         </is>
       </c>
-      <c r="B51" s="35" t="n"/>
-      <c r="C51" s="35" t="n"/>
-      <c r="D51" s="35" t="n"/>
-      <c r="E51" s="36" t="n">
+      <c r="B49" s="37" t="n"/>
+      <c r="C49" s="37" t="n"/>
+      <c r="D49" s="37" t="n"/>
+      <c r="E49" s="38" t="n">
         <v>0.1</v>
       </c>
-      <c r="F51" s="37">
-        <f>ROUND(F50*E51,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="38" t="inlineStr">
+      <c r="F49" s="39">
+        <f>ROUND(F48*E49,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="40" t="inlineStr">
         <is>
           <t>TỔNG CỘNG THANH TOÁN / 付款总额</t>
         </is>
       </c>
-      <c r="B52" s="38" t="n"/>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="38" t="n"/>
-      <c r="E52" s="38" t="n"/>
-      <c r="F52" s="39">
-        <f>F50+F51</f>
-        <v/>
-      </c>
-      <c r="G52" s="40" t="n"/>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="41" t="inlineStr">
+      <c r="B50" s="40" t="n"/>
+      <c r="C50" s="40" t="n"/>
+      <c r="D50" s="40" t="n"/>
+      <c r="E50" s="40" t="n"/>
+      <c r="F50" s="41">
+        <f>F48+F49</f>
+        <v/>
+      </c>
+      <c r="G50" s="42" t="n"/>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="43" t="inlineStr">
         <is>
           <t>Bằng chữ: Ba tỷ ba trăm bảy mươi chín triệu sáu trăm chín mươi ba nghìn ba trăm năm mươi đồng.
 大写金额：叁拾叁亿柒仟玖佰陆拾玖万叁仟叁佰伍拾越南盾整</t>
         </is>
       </c>
-      <c r="B53" s="41" t="n"/>
-      <c r="C53" s="41" t="n"/>
-      <c r="D53" s="41" t="n"/>
-      <c r="E53" s="41" t="n"/>
-      <c r="F53" s="41" t="n"/>
-      <c r="G53" s="41" t="n"/>
-    </row>
-    <row r="54" ht="12" customHeight="1"/>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="42" t="inlineStr">
+      <c r="B51" s="43" t="n"/>
+      <c r="C51" s="43" t="n"/>
+      <c r="D51" s="43" t="n"/>
+      <c r="E51" s="43" t="n"/>
+      <c r="F51" s="43" t="n"/>
+      <c r="G51" s="43" t="n"/>
+    </row>
+    <row r="52" ht="12" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="44" t="inlineStr">
         <is>
           <t>ĐIỀU KHOẢN THƯƠNG MẠI / 商务条款</t>
         </is>
       </c>
-      <c r="B55" s="42" t="n"/>
-      <c r="C55" s="42" t="n"/>
-      <c r="D55" s="42" t="n"/>
-      <c r="E55" s="42" t="n"/>
-      <c r="F55" s="42" t="n"/>
-      <c r="G55" s="42" t="n"/>
-    </row>
-    <row r="56" ht="42.5" customHeight="1">
-      <c r="A56" s="43" t="inlineStr">
+      <c r="B53" s="44" t="n"/>
+      <c r="C53" s="44" t="n"/>
+      <c r="D53" s="44" t="n"/>
+      <c r="E53" s="44" t="n"/>
+      <c r="F53" s="44" t="n"/>
+      <c r="G53" s="44" t="n"/>
+    </row>
+    <row r="54" ht="42.5" customHeight="1">
+      <c r="A54" s="45" t="inlineStr">
         <is>
           <t>1. Đơn giá trên đã bao gồm vật tư và nhân công lắp đặt, chưa bao gồm thuế GTGT. Khối lượng quyết toán theo thực tế thi công. Toàn bộ cáp điện là cáp lõi đồng.
     以上单价已含材料费及人工安装费，不含增值税。工程量按实际结算。本项目所有电缆均为铜芯电缆。</t>
         </is>
       </c>
-      <c r="B56" s="43" t="n"/>
-      <c r="C56" s="43" t="n"/>
-      <c r="D56" s="43" t="n"/>
-      <c r="E56" s="43" t="n"/>
-      <c r="F56" s="43" t="n"/>
-      <c r="G56" s="43" t="n"/>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="43" t="inlineStr">
+      <c r="B54" s="45" t="n"/>
+      <c r="C54" s="45" t="n"/>
+      <c r="D54" s="45" t="n"/>
+      <c r="E54" s="45" t="n"/>
+      <c r="F54" s="45" t="n"/>
+      <c r="G54" s="45" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="45" t="inlineStr">
         <is>
           <t>2. Hiệu lực báo giá: 30 ngày kể từ ngày báo giá.
     报价有效期：自报价之日起30天。</t>
         </is>
       </c>
-      <c r="B57" s="43" t="n"/>
-      <c r="C57" s="43" t="n"/>
-      <c r="D57" s="43" t="n"/>
-      <c r="E57" s="43" t="n"/>
-      <c r="F57" s="43" t="n"/>
-      <c r="G57" s="43" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="43" t="inlineStr">
+      <c r="B55" s="45" t="n"/>
+      <c r="C55" s="45" t="n"/>
+      <c r="D55" s="45" t="n"/>
+      <c r="E55" s="45" t="n"/>
+      <c r="F55" s="45" t="n"/>
+      <c r="G55" s="45" t="n"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="45" t="inlineStr">
         <is>
           <t>3. Thời gian giao hàng: theo tiến độ thi công thống nhất giữa hai bên.
     交货时间：按双方确认的施工进度。</t>
         </is>
       </c>
-      <c r="B58" s="43" t="n"/>
-      <c r="C58" s="43" t="n"/>
-      <c r="D58" s="43" t="n"/>
-      <c r="E58" s="43" t="n"/>
-      <c r="F58" s="43" t="n"/>
-      <c r="G58" s="43" t="n"/>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="43" t="inlineStr">
+      <c r="B56" s="45" t="n"/>
+      <c r="C56" s="45" t="n"/>
+      <c r="D56" s="45" t="n"/>
+      <c r="E56" s="45" t="n"/>
+      <c r="F56" s="45" t="n"/>
+      <c r="G56" s="45" t="n"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="45" t="inlineStr">
         <is>
           <t>4. Địa điểm giao hàng: tại công trình MEGA.
     交货地点：MEGA项目现场。</t>
         </is>
       </c>
-      <c r="B59" s="43" t="n"/>
-      <c r="C59" s="43" t="n"/>
-      <c r="D59" s="43" t="n"/>
-      <c r="E59" s="43" t="n"/>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="43" t="inlineStr">
+      <c r="B57" s="45" t="n"/>
+      <c r="C57" s="45" t="n"/>
+      <c r="D57" s="45" t="n"/>
+      <c r="E57" s="45" t="n"/>
+      <c r="F57" s="45" t="n"/>
+      <c r="G57" s="45" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="45" t="inlineStr">
         <is>
           <t>5. Thanh toán: chuyển khoản, theo tiến độ thỏa thuận trong hợp đồng.
     付款方式：银行转账，按合同约定的进度付款。</t>
         </is>
       </c>
-      <c r="B60" s="43" t="n"/>
-      <c r="C60" s="43" t="n"/>
-      <c r="D60" s="43" t="n"/>
-      <c r="E60" s="43" t="n"/>
-      <c r="F60" s="43" t="n"/>
-      <c r="G60" s="43" t="n"/>
-    </row>
-    <row r="61" ht="42.5" customHeight="1">
-      <c r="A61" s="43" t="inlineStr">
+      <c r="B58" s="45" t="n"/>
+      <c r="C58" s="45" t="n"/>
+      <c r="D58" s="45" t="n"/>
+      <c r="E58" s="45" t="n"/>
+      <c r="F58" s="45" t="n"/>
+      <c r="G58" s="45" t="n"/>
+    </row>
+    <row r="59" ht="42.5" customHeight="1">
+      <c r="A59" s="45" t="inlineStr">
         <is>
           <t>6. Thông tin chuyển khoản: Số TK 1066217478 – Ngân hàng TMCP Ngoại thương Việt Nam (Vietcombank) – Chủ tài khoản: CT TNHH KY THUAT CONG TRINH BLT.
     银行账户：1066217478，户名：CT TNHH KY THUAT CONG TRINH BLT。</t>
         </is>
       </c>
-      <c r="B61" s="43" t="n"/>
-      <c r="C61" s="43" t="n"/>
-      <c r="D61" s="43" t="n"/>
-      <c r="E61" s="43" t="n"/>
-      <c r="F61" s="43" t="n"/>
-      <c r="G61" s="43" t="n"/>
-    </row>
-    <row r="62" ht="6" customHeight="1"/>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="17" t="inlineStr">
+      <c r="B59" s="45" t="n"/>
+      <c r="C59" s="45" t="n"/>
+      <c r="D59" s="45" t="n"/>
+      <c r="E59" s="45" t="n"/>
+      <c r="F59" s="45" t="n"/>
+      <c r="G59" s="45" t="n"/>
+    </row>
+    <row r="60" ht="6" customHeight="1"/>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>Rất mong nhận được sự hợp tác của Quý khách. Trân trọng!
 期待与贵方合作，此致敬礼！</t>
         </is>
       </c>
-      <c r="B63" s="17" t="n"/>
-      <c r="C63" s="17" t="n"/>
-      <c r="D63" s="17" t="n"/>
-      <c r="E63" s="17" t="n"/>
-      <c r="F63" s="17" t="n"/>
-      <c r="G63" s="17" t="n"/>
-    </row>
-    <row r="64" ht="12" customHeight="1"/>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="44" t="inlineStr">
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="19" t="n"/>
+      <c r="G61" s="19" t="n"/>
+    </row>
+    <row r="62" ht="12" customHeight="1"/>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="46" t="inlineStr">
         <is>
           <t>XÁC NHẬN CỦA KHÁCH HÀNG
 客户确认</t>
         </is>
       </c>
-      <c r="B65" s="44" t="n"/>
-      <c r="C65" s="44" t="n"/>
-      <c r="E65" s="44" t="inlineStr">
+      <c r="B63" s="46" t="n"/>
+      <c r="C63" s="46" t="n"/>
+      <c r="E63" s="46" t="inlineStr">
         <is>
           <t>GIÁM ĐỐC
 总经理</t>
         </is>
       </c>
-      <c r="F65" s="44" t="n"/>
-      <c r="G65" s="44" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="45" t="inlineStr">
+      <c r="F63" s="46" t="n"/>
+      <c r="G63" s="46" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>(Ký, ghi rõ họ tên) （签字并注明姓名）</t>
         </is>
       </c>
-      <c r="B66" s="45" t="n"/>
-      <c r="C66" s="45" t="n"/>
-      <c r="E66" s="45" t="inlineStr">
+      <c r="B64" s="47" t="n"/>
+      <c r="C64" s="47" t="n"/>
+      <c r="E64" s="47" t="inlineStr">
         <is>
           <t>(Ký, đóng dấu, ghi rõ họ tên) （签字盖章并注明姓名）</t>
         </is>
       </c>
-      <c r="F66" s="45" t="n"/>
-      <c r="G66" s="45" t="n"/>
-    </row>
+      <c r="F64" s="47" t="n"/>
+      <c r="G64" s="47" t="n"/>
+    </row>
+    <row r="65" ht="16" customHeight="1"/>
+    <row r="66" ht="16" customHeight="1"/>
     <row r="67" ht="16" customHeight="1"/>
     <row r="68" ht="16" customHeight="1"/>
-    <row r="69" ht="16" customHeight="1"/>
-    <row r="70" ht="16" customHeight="1"/>
-    <row r="71" ht="20" customHeight="1">
-      <c r="E71" s="46" t="inlineStr">
+    <row r="69" ht="20" customHeight="1">
+      <c r="E69" s="48" t="inlineStr">
         <is>
           <t>HỒ VĂN BÌNH</t>
         </is>
       </c>
-      <c r="F71" s="46" t="n"/>
-      <c r="G71" s="46" t="n"/>
+      <c r="F69" s="48" t="n"/>
+      <c r="G69" s="48" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A66:C66"/>
+  <mergeCells count="43">
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="A48:E48"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="B1:D1"/>
     <mergeCell ref="A53:G53"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="E9:G9"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="E2:G2"/>
     <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A9:G9"/>
     <mergeCell ref="E11:G11"/>
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A50:E50"/>
+    <mergeCell ref="B5:D5"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A61:G61"/>
-    <mergeCell ref="E66:G66"/>
-    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A9:C9"/>
     <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="E71:G71"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="B22:G22"/>
     <mergeCell ref="A56:G56"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="E5:G5"/>
     <mergeCell ref="A55:G55"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E64:G64"/>
     <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E1:G1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.6" header="0.5" footer="0.25"/>
@@ -2301,7 +2364,7 @@
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="49" min="0" max="16383" man="1"/>
+    <brk id="44" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
